--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2021_T3_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2021_T3_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="49">
   <si>
     <t/>
   </si>
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>71</t>
+    <t>65</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,37 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.296</t>
-  </si>
-  <si>
-    <t>(0.055)</t>
-  </si>
-  <si>
-    <t>0.549</t>
-  </si>
-  <si>
-    <t>(0.059)</t>
-  </si>
-  <si>
-    <t>0.282</t>
-  </si>
-  <si>
-    <t>(0.054)</t>
-  </si>
-  <si>
-    <t>0.986</t>
-  </si>
-  <si>
-    <t>(0.347)</t>
-  </si>
-  <si>
-    <t>1.465</t>
-  </si>
-  <si>
-    <t>(0.241)</t>
-  </si>
-  <si>
-    <t>0.408</t>
-  </si>
-  <si>
-    <t>(0.089)</t>
+    <t>0.323</t>
+  </si>
+  <si>
+    <t>(0.058)</t>
+  </si>
+  <si>
+    <t>0.600</t>
+  </si>
+  <si>
+    <t>(0.061)</t>
+  </si>
+  <si>
+    <t>0.308</t>
+  </si>
+  <si>
+    <t>1.077</t>
+  </si>
+  <si>
+    <t>(0.377)</t>
+  </si>
+  <si>
+    <t>1.600</t>
+  </si>
+  <si>
+    <t>(0.256)</t>
+  </si>
+  <si>
+    <t>0.446</t>
+  </si>
+  <si>
+    <t>(0.096)</t>
   </si>
   <si>
     <t>45</t>
@@ -132,13 +129,10 @@
     <t>(0.559)</t>
   </si>
   <si>
-    <t>1.600</t>
-  </si>
-  <si>
     <t>(0.299)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +144,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.126</t>
-  </si>
-  <si>
-    <t>0.317***</t>
-  </si>
-  <si>
-    <t>0.341***</t>
-  </si>
-  <si>
-    <t>0.459</t>
-  </si>
-  <si>
-    <t>2.669***</t>
-  </si>
-  <si>
-    <t>1.192***</t>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>0.267***</t>
+  </si>
+  <si>
+    <t>0.315***</t>
+  </si>
+  <si>
+    <t>0.368</t>
+  </si>
+  <si>
+    <t>2.533***</t>
+  </si>
+  <si>
+    <t>1.154***</t>
   </si>
 </sst>
 </file>
@@ -226,13 +220,13 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -249,13 +243,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -278,7 +272,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -292,16 +286,16 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -318,7 +312,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -338,16 +332,16 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -364,7 +358,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -384,16 +378,16 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -404,13 +398,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -427,19 +421,19 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -450,13 +444,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -473,19 +467,19 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -496,13 +490,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -519,19 +513,19 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
         <v>39</v>
       </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -542,13 +536,13 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
